--- a/fase_de_desarrollo/manual_carga_masiva_postura/Plantilla_SANTA_REYES_PRODUCCION.xlsx
+++ b/fase_de_desarrollo/manual_carga_masiva_postura/Plantilla_SANTA_REYES_PRODUCCION.xlsx
@@ -5,19 +5,21 @@
     <workbookView activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="5" r:id="rId6"/>
-    <sheet name="Ejemplo" sheetId="6" r:id="rId7"/>
+    <sheet name="Instrucciones" sheetId="7" r:id="rId8"/>
+    <sheet name="Ejemplo" sheetId="8" r:id="rId9"/>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
     <sheet name="Alimento" sheetId="2" r:id="rId3"/>
     <sheet name="Movimientos Aves" sheetId="3" r:id="rId4"/>
-    <sheet name="Referencias" sheetId="4" r:id="rId5"/>
+    <sheet name="Movimientos Huevos" sheetId="4" r:id="rId5"/>
+    <sheet name="Huevos" sheetId="5" r:id="rId6"/>
+    <sheet name="Referencias" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
   <si>
     <t>Fecha</t>
   </si>
@@ -145,12 +147,27 @@
     <t>Motivo</t>
   </si>
   <si>
+    <t>Ítem</t>
+  </si>
+  <si>
+    <t>Tipo Destino</t>
+  </si>
+  <si>
+    <t>Destino</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
     <t>Alimento (nombre)</t>
   </si>
   <si>
     <t>Código</t>
   </si>
   <si>
+    <t>Ítem huevo (nombre)</t>
+  </si>
+  <si>
     <t>Lote producción (nombre)</t>
   </si>
   <si>
@@ -169,6 +186,15 @@
     <t>1307</t>
   </si>
   <si>
+    <t>HUEVO MANCHADO ROJO</t>
+  </si>
+  <si>
+    <t>538</t>
+  </si>
+  <si>
+    <t>Pnc</t>
+  </si>
+  <si>
     <t>LOTE 218A</t>
   </si>
   <si>
@@ -187,6 +213,15 @@
     <t>1308</t>
   </si>
   <si>
+    <t>HUEVO SIN CLASIFICAR ROJO</t>
+  </si>
+  <si>
+    <t>528</t>
+  </si>
+  <si>
+    <t>Primera</t>
+  </si>
+  <si>
     <t>GR HUEVO FASE II SR H</t>
   </si>
   <si>
@@ -496,7 +531,7 @@
     <t>• Si el archivo consume más de lo que hay EN ESE SILO, se rechaza ENTERO indicando cuánto falta.</t>
   </si>
   <si>
-    <t>• Huevos: esta empresa los clasifica por ítem del catálogo. Etapa: 1, 2 o 3.</t>
+    <t>• Huevos: el desglose va en la hoja 'Huevos', por ítem del catálogo. El total del día se calcula de esas filas. Etapa: 1, 2 o 3.</t>
   </si>
   <si>
     <t>• Esta empresa no maneja machos en postura: la plantilla no trae ninguna columna de machos. No las agregues a mano.</t>
@@ -508,13 +543,22 @@
     <t>• No cargues en 'Movimientos Aves' movimientos que ya se registraron por pantalla, ni repitas la misma fila: se duplicarían. Dos movimientos iguales el mismo día van como una sola fila sumada.</t>
   </si>
   <si>
-    <t>• Los traslados a planta y las ventas de huevo de esta empresa se cargan por pantalla, no por Excel: la hoja 'Movimientos Huevos' solo entiende las 11 categorías fijas, que acá no se usan.</t>
+    <t>• Hoja 'Movimientos Huevos': salidas de huevos de ESTE lote, UNA FILA POR TIPO DE HUEVO. 'Traslado' = envío a planta; 'Venta' = venta (con 'Motivo' y 'Descripción').</t>
+  </si>
+  <si>
+    <t>• Las filas que comparten fecha, tipo y destino forman UN movimiento con varios tipos de huevo. Para cargar dos movimientos distintos el mismo día, diferencialos por destino, motivo o descripción.</t>
+  </si>
+  <si>
+    <t>• Solo se aceptan los tipos de huevo declarados por este lote (los de la hoja 'Referencias'), y no podés mover más de lo producido de cada tipo.</t>
   </si>
   <si>
     <t>• Pesaje y agua: 'Peso H/M (g)', 'Uniformidad', 'Coef. Variación', 'Observaciones Pesaje', 'Consumo Agua (L)', 'pH Agua' (0-14), 'ORP Agua (mV)' y 'Temperatura Agua (°C)' son opcionales y se guardan tal cual en el registro del día.</t>
   </si>
   <si>
-    <t>⚠ Este lote todavía NO declaró qué tipos de huevo produce, así que la plantilla no trae la hoja 'Huevos'. Editá el lote, declará sus tipos de huevo y volvé a descargar la plantilla.</t>
+    <t>• Hoja 'Huevos': clasificación por ítem del catálogo (una fila por fecha e ítem). No la combines con las 11 categorías de la hoja 'Datos'.</t>
+  </si>
+  <si>
+    <t>• El desplegable de 'Ítem' trae SOLO los tipos de huevo declarados por este lote. Cada fecha de la hoja 'Huevos' tiene que existir también en 'Datos'.</t>
   </si>
   <si>
     <t>ORDEN DE CARGA (importa)</t>
@@ -695,6 +739,27 @@
   </si>
   <si>
     <t>• Esta empresa no maneja machos en postura: dejá «Machos» vacío.</t>
+  </si>
+  <si>
+    <t>Hoja «Huevos»</t>
+  </si>
+  <si>
+    <t>7900</t>
+  </si>
+  <si>
+    <t>550</t>
+  </si>
+  <si>
+    <t>• Varias filas por fecha: una por tipo de huevo. El total del día se calcula sumándolas.</t>
+  </si>
+  <si>
+    <t>• Cada fecha de esta hoja tiene que existir también en la hoja «Datos».</t>
+  </si>
+  <si>
+    <t>• Solo se aceptan los tipos de huevo DECLARADOS POR EL LOTE. Si el desplegable viene vacío, editá el lote y declará qué tipos produce antes de usar esta hoja.</t>
+  </si>
+  <si>
+    <t>• No la combines con las 11 categorías fijas: cargar las dos fuentes el mismo día es un error.</t>
   </si>
 </sst>
 </file>
@@ -855,7 +920,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" sqref="G2:G1000" xr:uid="{F3ACC421-3828-4AA0-8E06-3D1F3E194A70}">
+    <dataValidation type="list" showErrorMessage="1" sqref="G2:G1000" xr:uid="{80B25C59-F9D7-4F94-9276-8BFBFDF26A2C}">
       <formula1>"kg,qq"</formula1>
     </dataValidation>
   </dataValidations>
@@ -863,25 +928,25 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{74F9045B-A1E1-4AEC-9F32-9CB1082F1640}">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{2362A5DA-F5F2-49B1-8200-60BF1FF80EAB}">
           <x14:formula1>
             <xm:f>Referencias!$A$2:$A$46</xm:f>
           </x14:formula1>
           <xm:sqref>H2:H1000</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{AECEBA6D-2DFF-402E-BDED-209DAE1FBE70}">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{A7AA69B8-8FFB-49D1-9D30-AF6BAA633209}">
           <x14:formula1>
             <xm:f>Referencias!$A$2:$A$46</xm:f>
           </x14:formula1>
           <xm:sqref>K2:K1000</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{B3E9C6AC-C68E-4438-9AC0-379130A99E91}">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{F0E5CFDB-D9C5-4E54-941C-FA83F3EB7096}">
           <x14:formula1>
             <xm:f>Referencias!$L$2:$L$2</xm:f>
           </x14:formula1>
           <xm:sqref>J2:J1000</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{58C03B1D-27C6-4469-BDD8-07986FD9F0AD}">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{9C71701C-7829-4190-9E58-89436DDB09F4}">
           <x14:formula1>
             <xm:f>Referencias!$L$2:$L$2</xm:f>
           </x14:formula1>
@@ -968,13 +1033,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" showErrorMessage="1" sqref="B2:B1000" xr:uid="{70A33572-2FD3-4F18-9566-B061441ECC7C}">
+    <dataValidation type="list" showErrorMessage="1" sqref="B2:B1000" xr:uid="{C364A511-F1D1-4E3B-9410-C89B34723A70}">
       <formula1>"Ingreso,Traslado,Recepción,Consumo"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" sqref="E2:E1000" xr:uid="{CD81977C-9E86-4E6E-824E-247EAB0C4165}">
+    <dataValidation type="list" showErrorMessage="1" sqref="E2:E1000" xr:uid="{DC543DBF-3A9F-44F6-AD11-7677FA388ED9}">
       <formula1>"kg,qq"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" sqref="N2:N1000" xr:uid="{B7E903F9-69EB-4281-A3F9-2005F01914BC}">
+    <dataValidation type="list" showErrorMessage="1" sqref="N2:N1000" xr:uid="{64C277CD-D328-4A59-8A18-FE99D7AFF87C}">
       <formula1>"planta,bodega,granja"</formula1>
     </dataValidation>
   </dataValidations>
@@ -982,19 +1047,19 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{3D140D2C-EA05-4507-A3B4-9B8813E40D95}">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{0E41B982-6700-44A2-A7EF-7ECC97C39355}">
           <x14:formula1>
             <xm:f>Referencias!$A$2:$A$46</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C1000</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{12B69173-C1EB-40C7-9855-915DF6508EFC}">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{2074ADFE-7FEA-465A-832D-F1C148A2B917}">
           <x14:formula1>
             <xm:f>Referencias!$L$2:$L$2</xm:f>
           </x14:formula1>
           <xm:sqref>I2:I1000</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{3F6434DE-26F6-47D5-ACDA-B79E66058D8C}">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{9E1CB563-3727-4AEE-A11F-934A0A4282AF}">
           <x14:formula1>
             <xm:f>Referencias!$L$2:$L$2</xm:f>
           </x14:formula1>
@@ -1049,7 +1114,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" sqref="B2:B1000" xr:uid="{B23F67F5-9355-4895-925F-141AA2FDD980}">
+    <dataValidation type="list" showErrorMessage="1" sqref="B2:B1000" xr:uid="{622BF4C9-CE53-4F12-8CA1-6F94AFC73032}">
       <formula1>"Salida,Ingreso,Venta"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1057,7 +1122,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{55A7248E-402B-4F04-84F8-A1E3AD4A9727}">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{E9B75569-BB0E-497A-8B08-83212C0B7114}">
           <x14:formula1>
             <xm:f>Referencias!$H$2:$H$2</xm:f>
           </x14:formula1>
@@ -1071,13 +1136,121 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.52771282196045" customWidth="1"/>
+    <col min="5" max="5" width="13.958294868469238" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="12.646622657775879" customWidth="1"/>
+    <col min="9" max="9" width="16.05777359008789" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" showErrorMessage="1" sqref="B2:B1000" xr:uid="{55E0F3D2-4CA0-49CC-BC75-57C2EC8ACCAB}">
+      <formula1>"Traslado,Venta"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" sqref="E2:E1000" xr:uid="{4C6823DC-ACCA-4CC0-B054-54B03AF18EDA}">
+      <formula1>"Planta,Cliente,Empresa"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{C4903AD1-6BAA-4220-8E5F-9206EE72A0F5}">
+          <x14:formula1>
+            <xm:f>Referencias!$D$2:$D$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C1000</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="9.52771282196045" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{F32BC313-A7FB-47BE-8A78-AC3A51DEA465}">
+          <x14:formula1>
+            <xm:f>Referencias!$D$2:$D$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1000</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.29553985595703" customWidth="1"/>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="29.573999404907227" customWidth="1"/>
     <col min="5" max="5" width="9.140625" customWidth="1"/>
     <col min="6" max="6" width="9.140625" customWidth="1"/>
     <col min="7" max="7" width="9.140625" customWidth="1"/>
@@ -1091,400 +1264,427 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>36</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J1" s="0" t="s">
         <v>26</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>49</v>
+        <v>54</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>57</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I2" s="0">
         <v>152</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="M2" s="0" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>55</v>
+        <v>63</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -1492,9 +1692,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="256" customWidth="1"/>
@@ -1502,162 +1702,177 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>170</v>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -1665,13 +1880,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="12.589447021484375" customWidth="1"/>
+    <col min="2" max="2" width="29.573999404907227" customWidth="1"/>
     <col min="3" max="3" width="18.1722469329834" customWidth="1"/>
     <col min="4" max="4" width="17.214269638061523" customWidth="1"/>
     <col min="5" max="5" width="17.576473236083984" customWidth="1"/>
@@ -1696,12 +1911,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4">
@@ -1774,178 +1989,178 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="N5" s="0" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="O5" s="0" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="P5" s="0" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="R5" s="0" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="S5" s="0" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="T5" s="0" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="U5" s="0" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="V5" s="0" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="B6" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="E6" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>180</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>176</v>
-      </c>
       <c r="G6" s="0" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="N6" s="0" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="S6" s="0" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="T6" s="0" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="U6" s="0" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="V6" s="0" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="C7" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="J7" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="N7" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="E7" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>195</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>178</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>196</v>
-      </c>
-      <c r="J7" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="N7" s="0" t="s">
-        <v>180</v>
-      </c>
       <c r="S7" s="0" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="T7" s="0" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="U7" s="0" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="V7" s="0" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18">
@@ -2000,56 +2215,56 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="N19" s="0" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="O19" s="0" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="P19" s="0" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28">
@@ -2080,58 +2295,116 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>225</v>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
